--- a/courses/powerBI/Power-BI-Lexicon.xlsx
+++ b/courses/powerBI/Power-BI-Lexicon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power BI Lexicon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Power BI Lexicon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power BI Lexicon'!$A$3:$C$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power BI Lexicon'!$A$3:$C$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>68 terms. Free course at impactmojo.in/courses/powerbi. Power BI is a Microsoft product; this course is independent.</t>
+          <t>93 terms. Free course at impactmojo.in/courses/powerbi. Power BI is a Microsoft product; this course is independent.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>The Power BI file format. A single file that can bundle the queries, the data model with its calculations, and the report pages, which makes a whole analysis portable.</t>
+          <t>The Power BI Desktop file format — a single file bundling the queries, the data model with its calculations, and the report pages, making a whole analysis portable.</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Fields pane</t>
+          <t>Desktop Views (Report, Data, Model)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -597,14 +597,14 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>The list on the right of every table, column and measure in your model. You drag from here onto visuals.</t>
+          <t>The three view icons on Desktop's left edge: Report view is the canvas for visuals, Data view shows the actual rows of loaded tables, and Model view is the diagram where relationships and the star schema are built.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Model view</t>
+          <t>Fields pane</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -614,14 +614,14 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>The diagram where tables and their relationships are shown and edited. The third view icon, where you build a star schema.</t>
+          <t>The list on the right of every table, column and measure in your model. You drag from here onto visuals.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Power BI Desktop</t>
+          <t>Model view</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -631,14 +631,14 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>The free Windows application where you connect to data, clean it, model it, write calculations and design reports. The whole of this course except sharing happens here.</t>
+          <t>The diagram where tables and their relationships are shown and edited. The third view icon, where you build a star schema.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Power BI Mobile</t>
+          <t>Power BI Desktop</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -648,14 +648,14 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>The phone and tablet apps for viewing published reports. A consumption surface, not an authoring one.</t>
+          <t>The free Windows application where reports are built — data ingestion, modelling, DAX, and visuals all happen here before publishing.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Power BI Service</t>
+          <t>Power BI Mobile</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -665,14 +665,14 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>The cloud at app.powerbi.com where finished reports are published and shared. Viewing and light editing work in any browser; publishing needs a paid licence.</t>
+          <t>The phone and tablet apps for viewing published reports. A consumption surface, not an authoring one.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Report view</t>
+          <t>Power BI Service</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -682,14 +682,14 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>The canvas where you build and arrange visuals. The first of the three view icons on the left edge.</t>
+          <t>The cloud platform (app.powerbi.com) where published reports live — sharing, refresh schedules, apps, and workspaces.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Ribbon</t>
+          <t>Report view</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -699,14 +699,14 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>The command bar across the top: Home, Insert, Modeling, View and others. Get Data and Refresh live on Home.</t>
+          <t>The canvas where you build and arrange visuals. The first of the three view icons on the left edge.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Visualizations pane</t>
+          <t>Ribbon</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -716,31 +716,31 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>The panel where you choose a chart type and drag fields into wells such as Axis, Values and Legend.</t>
+          <t>The command bar across the top: Home, Insert, Modeling, View and others. Get Data and Refresh live on Home.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Append</t>
+          <t>Visualizations pane</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Get Data &amp; Power Query</t>
+          <t>Interface &amp; files</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Stack the rows of two queries into one, a union. Used to combine survey rounds into one long table.</t>
+          <t>The panel where you choose a chart type and drag fields into wells such as Axis, Values and Legend.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Applied Steps</t>
+          <t>Append</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -750,14 +750,14 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>The ordered list of every transformation applied to a query. An audit trail and a recipe that re-runs on each refresh.</t>
+          <t>Stack the rows of two queries into one, a union. Used to combine survey rounds into one long table.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Change type</t>
+          <t>Append vs Merge</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -767,14 +767,14 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Set a column's data type, such as decimal number or text. Wrong types are the most common cause of broken totals.</t>
+          <t>Append stacks tables with the same columns (months of exports); Merge joins tables on a key (like VLOOKUP, but robust).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Close &amp; Apply</t>
+          <t>Applied Steps</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -784,14 +784,14 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>The command that exits Power Query and loads the cleaned tables into the model.</t>
+          <t>The ordered, editable list of transformations in Power Query — your cleaning recipe, visible and auditable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Change type</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -801,14 +801,14 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>A built-in method for reading a particular kind of source, such as the Excel, CSV or Web connector.</t>
+          <t>Set a column's data type, such as decimal number or text. Wrong types are the most common cause of broken totals.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Filter rows</t>
+          <t>Close &amp; Apply</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Drop unwanted rows in Power Query, such as blanks, footnotes or a Total row that would double-count.</t>
+          <t>The command that exits the Power Query editor and loads the cleaned, transformed tables into the data model. Until it runs, transformations exist only as steps, not as loaded data.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Get Data</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -835,14 +835,14 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>The Home-ribbon entry point to over a hundred connectors: Excel, Text/CSV, Web, databases and more. Where every project begins.</t>
+          <t>A built-in method for reading a particular kind of source, such as the Excel, CSV or Web connector.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Load</t>
+          <t>Data Source</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -852,14 +852,14 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>The button that brings data straight into the model as-is, skipping cleaning. Usually the wrong default.</t>
+          <t>Where data comes from — Excel, CSV, databases, SharePoint, web APIs, Google Sheets — each with its own connector and credential needs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>M language</t>
+          <t>Data Type</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>The functional language behind Power Query. Each Applied Step is M code; the Advanced Editor shows it.</t>
+          <t>The declared type of each column — text, whole number, decimal, date — the first thing to fix, and the source of most silent errors.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Merge</t>
+          <t>Filter rows</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -886,14 +886,14 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Join two queries by a matching key, bringing columns from one into the other. Supports left, inner, full outer and anti-joins.</t>
+          <t>Drop unwanted rows in Power Query, such as blanks, footnotes or a Total row that would double-count.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Power Query Editor</t>
+          <t>Get Data</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -903,14 +903,14 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>The environment for cleaning and reshaping data through a recorded sequence of steps.</t>
+          <t>The Home-ribbon entry point to over a hundred connectors: Excel, Text/CSV, Web, databases and more. Where every project begins.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Promote headers</t>
+          <t>Import vs DirectQuery</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -920,14 +920,14 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Turn the first row of values into column names. Common after removing a stray title row from a government export.</t>
+          <t>Import copies data into the model (fast, offline, refresh needed); DirectQuery queries the source live (fresh, slower, source-dependent).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Reference vs Duplicate</t>
+          <t>Load</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Reference creates a query that points at another and follows its changes; Duplicate makes an independent copy.</t>
+          <t>The button that brings data straight into the model as-is, skipping cleaning. Usually the wrong default.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Replace values</t>
+          <t>M language</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Swap one value for another across a column, such as turning the text NA into a true null.</t>
+          <t>The formula language behind Power Query steps — usually written for you, editable when you need more than the UI offers.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Split column</t>
+          <t>Merge</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -971,14 +971,14 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Break one column into several by a delimiter, such as separating State and District from a combined label.</t>
+          <t>Join two queries by a matching key, bringing columns from one into the other. Supports left, inner, full outer and anti-joins.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Transform Data</t>
+          <t>Power Query Editor</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -988,14 +988,14 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>The button that opens the Power Query Editor so you can clean before loading. Usually the right default.</t>
+          <t>The data-preparation engine (Get Data → Transform): every cleaning step is recorded and replayed on each refresh.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Trim and Clean</t>
+          <t>Promote headers</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1005,14 +1005,14 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Transformations that remove leading and trailing spaces (Trim) and non-printing characters (Clean), fixing keys that look equal but are not.</t>
+          <t>Turn the first row of values into column names. Common after removing a stray title row from a government export.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Unpivot</t>
+          <t>Query Folding</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Reshape a wide table (one column per indicator) into a long one (one row per observation). The key move for survey factsheets.</t>
+          <t>Power Query pushing transformations back to the source database to execute — crucial for performance on large tables.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Unpivot Other Columns</t>
+          <t>Reference vs Duplicate</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1039,116 +1039,116 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Unpivot everything except a chosen key column, so newly added indicators flow in automatically on future files.</t>
+          <t>Two ways to copy a query: Reference creates a query that points at another and follows its changes; Duplicate makes a fully independent copy. Choosing wrong causes silent divergence or surprise breakage later.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Cardinality</t>
+          <t>Replace values</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>The nature of a relationship: usually one-to-many, from a dimension to the fact table.</t>
+          <t>Swap one value for another across a column, such as turning the text NA into a true null.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Cross-filter direction</t>
+          <t>Split column</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Which way a filter flows across a relationship. Single is the safe default; bidirectional only for a named need.</t>
+          <t>Break one column into several by a delimiter, such as separating State and District from a combined label.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Date table</t>
+          <t>Transform Data</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>A dedicated table with one continuous row per period, marked as a date table, required for reliable time intelligence.</t>
+          <t>The button that opens the Power Query Editor so you can clean before loading. Usually the right default.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Dimension table</t>
+          <t>Trim and Clean</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>A table of descriptive context, each item listed once, such as a District or Date table. What you slice and group by.</t>
+          <t>Transformations that remove leading and trailing spaces (Trim) and non-printing characters (Clean), fixing keys that look equal but are not.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Fact table</t>
+          <t>Unpivot</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>The table of events or measurements, one row per observation, holding the numbers you aggregate and keys to the dimensions.</t>
+          <t>Turning wide, human-formatted columns (Jan, Feb, Mar…) into tidy long data (Month, Value) that models and charts need.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Unpivot Other Columns</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Modelling</t>
+          <t>Get Data &amp; Power Query</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>The column used to match rows across tables in a relationship, such as a district code. Must share type and be clean.</t>
+          <t>Unpivot everything except a chosen key column, so newly added indicators flow in automatically on future files.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Cardinality</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -1158,14 +1158,14 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>A defined link between two tables on a shared key, letting filters and calculations flow between them.</t>
+          <t>The nature of a relationship — one-to-many (ideal), one-to-one, or many-to-many (avoid unless you know why).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Star schema</t>
+          <t>Cross-filter direction</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1175,150 +1175,150 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>A model with one central fact table joined to surrounding dimension tables. The shape to aim for in nearly all cases.</t>
+          <t>Which way a filter flows across a relationship. Single direction (dimension filters fact) is the safe default; bidirectional filtering should be enabled only for a specific, named need because it invites ambiguity and performance problems.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>CALCULATE</t>
+          <t>Date table</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>The central DAX function: it evaluates a measure while modifying the filter context, which is how comparisons are built.</t>
+          <t>A dedicated calendar table marked as such — a prerequisite for reliable time intelligence.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Calculated column</t>
+          <t>Dimension table</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>A calculation evaluated row by row at refresh and stored in the table. Used sparingly, for things like a classification flag.</t>
+          <t>Descriptive lookup tables — one row per entity — used to slice facts: districts, facilities, cadres, schemes.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Fact table</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Data Analysis Expressions, the formula language for calculations. Looks like Excel formulas; behaves differently.</t>
+          <t>The table of measurable events — one row per training session, disbursement, or survey response — usually long and narrow.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>DISTINCTCOUNT</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Counts the unique values in a column, such as how many distinct districts reported.</t>
+          <t>The column used to match rows across tables in a relationship, such as a district code. Must share type and be clean.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>DIVIDE</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Safe division that returns blank instead of an error when the denominator is zero. Use it instead of the slash, always.</t>
+          <t>The link between tables on a key column, letting filters flow from dimensions to facts.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>Semantic Model</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Returns a filtered table, often used inside CALCULATE for conditions a simple equals cannot express.</t>
+          <t>The published dataset — tables, relationships, and measures — that reports connect to; one model can feed many reports.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Filter context</t>
+          <t>Star schema</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>The set of filters active when a measure is evaluated, set by slicers, the visual, and any CALCULATE around it.</t>
+          <t>The recommended model shape: a central fact table (events, transactions) linked to dimension tables (who, where, when, what).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Measure</t>
+          <t>Surrogate Key</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Modelling</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>A calculation evaluated on demand against the current filter context, not stored. The right tool for rates, totals and shares.</t>
+          <t>A clean, unique identifier added when natural keys are messy — names change; ids shouldn't.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Row context</t>
+          <t>CALCULATE</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -1328,14 +1328,14 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>The single-row perspective in which a calculated column is evaluated.</t>
+          <t>The most important DAX function: evaluates an expression under modified filters — the key to 'of which', shares, and comparisons.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SUM / AVERAGE</t>
+          <t>Calculated column</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -1345,14 +1345,14 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Basic aggregate functions over a column.</t>
+          <t>A DAX column computed row by row and stored in the model — use for slicers/labels, not aggregations.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Time intelligence</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -1362,14 +1362,14 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Calculations comparing periods, such as change between survey rounds, which depend on a proper date table.</t>
+          <t>Data Analysis Expressions — the formula language for measures and calculated columns; Excel-like syntax, database-like thinking.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>VAR / RETURN</t>
+          <t>DISTINCTCOUNT</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -1379,335 +1379,760 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Variables in a DAX expression, used to make multi-step measures readable and to compute a value once.</t>
+          <t>Counts the unique values in a column, such as how many distinct districts reported.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Alt text</t>
+          <t>DIVIDE</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>A written description of a visual for screen readers and accessibility, part of responsible report design.</t>
+          <t>Safe division with a built-in alternative for divide-by-zero — use instead of the / operator in measures.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Encodes magnitude as length, read accurately. The default for comparing categories; sort it for an instant ranking.</t>
+          <t>Returns a filtered table, often used inside CALCULATE for conditions a simple equals cannot express.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Filter context</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>A visual showing one big headline number, such as a national rate.</t>
+          <t>The set of filters (from slicers, axes, and rows) under which a measure evaluates — the concept that explains most DAX surprises.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Choropleth / filled map</t>
+          <t>Implicit vs Explicit Measures</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>A map shading regions by a value. Map a rate, not a raw count, or it mostly shows where people live.</t>
+          <t>Dragging a numeric field creates an implicit aggregation; writing a named measure is explicit — explicit wins for consistency and reuse.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Conditional formatting</t>
+          <t>Iterators (SUMX family)</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Colouring values by a rule, such as turning districts above a threshold amber. Updates as data refreshes.</t>
+          <t>Functions that walk a table row by row applying an expression — needed when the maths must happen before aggregation.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Measure</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Encodes change over an ordered axis such as time. Not for unordered categories.</t>
+          <t>A DAX calculation evaluated at query time within the current filter context — the right default for any aggregation.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Matrix / table</t>
+          <t>Row context</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Visuals for exact values across one or two dimensions, when the reader needs numbers rather than a shape.</t>
+          <t>The 'current row' during calculated-column evaluation or inside iterators — distinct from filter context, and the second classic confusion.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Slicer</t>
+          <t>SUM / AVERAGE</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>An on-canvas control that filters the page, such as a state selector.</t>
+          <t>Basic aggregate functions over a column.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Truncated axis</t>
+          <t>Time intelligence</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Visualisation</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>A value axis that does not start at zero, which exaggerates differences. Avoid for bar charts.</t>
+          <t>DAX patterns over a date table — YTD, previous period, moving averages — for trend reporting.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Bookmark</t>
+          <t>VAR / RETURN</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>A saved page state (filters and visibility) that a button can trigger, used to build view toggles.</t>
+          <t>Named intermediate results inside a measure — for readability, performance, and debugging.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Cross-filtering</t>
+          <t>Alt text</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Clicking a data point in one visual filters the others on the page. On by default; tunable via Edit interactions.</t>
+          <t>A written description attached to a visual for screen readers — part of accessible, responsible report design alongside colour contrast and tab order.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>DPDP Act, 2023</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>India's Digital Personal Data Protection Act, governing digital personal data. Favour aggregates and keep identifiable records off shared artifacts.</t>
+          <t>Encodes magnitude as length, read accurately. The default for comparing categories; sort it for an instant ranking.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Drill-through</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>A right-click jump to a dedicated detail page that carries the selected item's filter.</t>
+          <t>A single-number visual for headline indicators — best with a target and a trend companion.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Export to PDF / PowerPoint</t>
+          <t>Chart Choice</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Free static export from Desktop, suitable for a board pack or email attachment.</t>
+          <t>Matching chart type to question — comparison (bars), trend (lines), distribution (histograms), part-to-whole (rarely pie).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Power BI Pro</t>
+          <t>Choropleth / filled map</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>The per-user licence (14 US dollars per month in 2026) needed to publish and to view shared reports outside large capacity.</t>
+          <t>A map shading regions by a value. Map a rate, not a raw count — otherwise the map mostly shows where people live rather than where the problem is.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Publish to web</t>
+          <t>Colour Accessibility</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>A free option that creates a fully public, unauthenticated link. For open content only, never for personal or sensitive data.</t>
+          <t>Palettes legible to colour-blind readers with sufficient contrast — meaning never carried by hue alone.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Report-page tooltip</t>
+          <t>Conditional formatting</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>A mini-page set as a hover tooltip, showing custom detail instead of a bare value.</t>
+          <t>Data-driven colour, icons, or bars in tables and visuals — encode meaning, don't decorate.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Row-level security (RLS)</t>
+          <t>Dashboard Ethics</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Report &amp; sharing</t>
+          <t>Visualisation</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Roles that restrict which rows a user sees. Defined in Desktop but only enforced once published with a paid licence.</t>
+          <t>Dashboards steer decisions: choose honest denominators, show uncertainty and data quality, resist vanity metrics.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
+          <t>Data-Ink Ratio</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Tufte's principle: maximise ink that carries data, delete decoration — the fastest route from cluttered to clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Drill-down</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Navigating a hierarchy within a visual — state to district to block — without leaving the chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Graphical Integrity</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Charts must not distort: axes start honestly, areas match magnitudes, baselines aren't truncated to exaggerate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Encodes change over an ordered axis such as time. Not for unordered categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Matrix / table</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Visuals for exact values across one or two dimensions, when the reader needs numbers rather than a shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Slicer</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>An on-canvas filter control users click — the main way non-analysts interrogate a report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Small Multiples</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Repeating one chart per category in a grid — honest comparison across many units without spaghetti lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Tooltip</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>The hover detail on a visual — customisable into a mini-report page for context without clutter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Truncated axis</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Visualisation</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>A value axis that does not start at zero, which exaggerates differences. Avoid for bar charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>App (Power BI)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>A packaged, read-only distribution of workspace content for an audience — the clean way to share with many viewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Bookmark</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>A saved view state (filters, visibility) wired to buttons — the building block of guided navigation and toggles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Cross-filtering</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Clicking a data point in one visual filters the other visuals on the page. It is on by default and tunable per visual pair via Edit Interactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Data Gateway</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Software bridging the cloud Service to on-premises sources so scheduled refresh can reach files and databases behind your firewall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>India's Digital Personal Data Protection Act, which governs the processing of digital personal data — including beneficiary records inside dashboards. Favour aggregates, minimise identifiable fields, and keep personal data off shared artifacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Drill-through</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>A right-click jump from a summary visual to a dedicated detail page that carries the selected item's filter with it. Distinct from drill-down, which descends a hierarchy inside one visual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Export to PDF / PowerPoint</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Free static export from Desktop, suitable for a board pack or an email attachment. It trades interactivity for reach — no licences, no logins, no refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Performance Analyzer</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Desktop's profiler showing per-visual query times — where to look when a report crawls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Power BI Pro</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>The per-user paid licence required to publish reports and to view content shared outside large dedicated capacity. Licensing, not technology, is often the real constraint for NGO dashboard rollouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Publish to web</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Public embedding that makes a report visible to anyone with the link — never for personal or beneficiary data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Report vs Dashboard</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>In Power BI terms: reports are multi-page canvases; dashboards are pinned-tile summaries in the Service — colloquially conflated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Report-page tooltip</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>A mini-page set as a hover tooltip, showing custom detail instead of a bare value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Row-level security (RLS)</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Model-defined roles that filter data per viewer — one report, each user seeing only their allowed rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Scheduled Refresh</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>The Service's timed re-import of data — the heartbeat of a live dashboard; failures mean silently stale numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Sensitivity &amp; Sharing Discipline</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Matching sharing method to data sensitivity — named access and RLS for personal data; aggregation before anything public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
           <t>Theme JSON</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Report &amp; sharing</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>A small file that sets palette and fonts across a whole report, the Power BI equivalent of design tokens.</t>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>A small JSON file that sets the palette, fonts, and defaults across a whole report — Power BI's version of design tokens, and the difference between consistent and hand-coloured dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Workspace</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Report &amp; sharing</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>The Service container where colleagues co-own content — dev/test/prod separation lives here.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C71"/>
+  <autoFilter ref="A3:C96"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
